--- a/uploads/resultado.xlsx
+++ b/uploads/resultado.xlsx
@@ -627,9 +627,11 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>45783</v>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -1115,9 +1117,11 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>45814</v>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -1557,28 +1561,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CAARAPO</t>
+          <t>ANTONIO JOAO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31176</v>
+        <v>19886</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NATALIA RAMOS DOS SANTOS</t>
+          <t>TANIA APARECIDA VALENSUELA MEDINA</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>45810</v>
+        <v>45783</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MARIANY TABORGA MARQUES</t>
+          <t>VENDAS DIGITAIS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ESCRITORIO CAARAPO</t>
+          <t>COB.PARCELA NOVOS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1587,19 +1591,17 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PADRAO ESCRITORIO</t>
+          <t>COB.PARCELA NOVOS</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>50</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>45810</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -1619,48 +1621,48 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CAARAPO</t>
+          <t>ARAL MOREIRA</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31177</v>
+        <v>20609</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MADALENA APARECIDA CORDEIRO</t>
+          <t>DANA REGINA DOS SANTOS</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>45811</v>
+        <v>45783</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MARIANY TABORGA MARQUES</t>
+          <t>MARLON DA SILVA LAURINDO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ESCRITORIO CAARAPO</t>
+          <t>COB.PARCELA NOVOS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>PLANO 03</t>
+          <t>PLANO 3</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PADRAO ESCRITORIO</t>
+          <t>COB.PARCELA NOVOS</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>50</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>45811</v>
+        <v>45814</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1685,15 +1687,15 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31178</v>
+        <v>31176</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLEITON DE ARAUJO SILVA</t>
+          <t>NATALIA RAMOS DOS SANTOS</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>45812</v>
+        <v>45810</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1702,7 +1704,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>COB.BOLETO BANCARIO</t>
+          <t>ESCRITORIO CAARAPO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1711,18 +1713,18 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PADRAO BOLETO</t>
+          <t>PADRAO ESCRITORIO</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>50</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>45812</v>
+        <v>45810</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1743,37 +1745,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DOURADINA</t>
+          <t>CAARAPO</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24072</v>
+        <v>31177</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLEONICE PEREIRA DA SILVA</t>
+          <t>MADALENA APARECIDA CORDEIRO</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>45812</v>
+        <v>45811</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VANUZA PONSONI</t>
+          <t>MARIANY TABORGA MARQUES</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>COB.ESCRITORIO DOURADINA</t>
+          <t>ESCRITORIO CAARAPO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PLANO LUXO</t>
+          <t>PLANO 03</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1781,9 +1783,11 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>45811</v>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -1794,58 +1798,42 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>CLEONICE PEREIRA DA SILVA</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Wellia de Sousa</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Televendas</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Filtro Inadimplente</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DOURADOS PRIMAVERA</t>
+          <t>CAARAPO</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>102544</v>
+        <v>31178</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GABRIEL FLEITAS DA SILVA</t>
+          <t>CLEITON DE ARAUJO SILVA</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>45810</v>
+        <v>45812</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ANDRESSA HONORIO PEREIRA</t>
+          <t>MARIANY TABORGA MARQUES</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PARCELAS NOVOS</t>
+          <t>COB.BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>PLANO 02 C 2 GAVETAS</t>
+          <t>PLANO 03</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1853,14 +1841,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PARCELAS NOVOS</t>
+          <t>PADRAO BOLETO</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>45811</v>
+        <v>45812</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1872,77 +1860,59 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>GABRIEL FLEITAS DA SILVA</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Andressa Honorio Pereira</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Televendas</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Indicação de Cliente</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DOURADOS PRIMAVERA</t>
+          <t>CASCAVEL</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>102545</v>
+        <v>13571</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MARIA APARECIDA SEABRA</t>
+          <t>EDSON LOPES DA ROCHA</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>45810</v>
+        <v>45783</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ANDRESSA HONORIO PEREIRA</t>
+          <t>JESSICA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO REGIAO 01</t>
+          <t>BOLETO CAIXA CASCAVEL</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>PLANO 03</t>
+          <t>PLANO 3</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO</t>
+          <t>PADRAO BOLETO CAIXA CASCAVEL</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>50</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>45811</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>NOVO</t>
+          <t>EM VIDA</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1950,77 +1920,59 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>MARIA APARECIDA SEABRA</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Andressa Honorio Pereira</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Televendas</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Indicação de Cliente</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DOURADOS PRIMAVERA</t>
+          <t>CASCAVEL</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>102552</v>
+        <v>13570</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MICHELE LILIANE PEREIRA</t>
+          <t>ANDREIA LOPES DA ROCHA</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>45811</v>
+        <v>45783</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>EDUARDA DE PAULA PASTOR VILELA</t>
+          <t>JESSICA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PARCELAS NOVOS</t>
+          <t>BOLETO CAIXA CASCAVEL</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PLANO 02 C 2 GAVETAS</t>
+          <t>PLANO 3</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PARCELAS NOVOS</t>
+          <t>PADRAO BOLETO CAIXA CASCAVEL</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>160</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>45812</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>NOVO</t>
+          <t>EM VIDA</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2028,74 +1980,56 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>MICHELE LILIANE PEREIRA DE CASTRO</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Lucas Dos Santos Delgado</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Sac</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Ligações</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DOURADOS PRIMAVERA</t>
+          <t>DOURADINA</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>102547</v>
+        <v>24072</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GISELI SILVA DE SOUZA</t>
+          <t>CLEONICE PEREIRA DA SILVA</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>45811</v>
+        <v>45812</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>EDUARDA DE PAULA PASTOR VILELA</t>
+          <t>VANUZA PONSONI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FUNCIONARIO GRUPO PAX</t>
+          <t>COB.ESCRITORIO DOURADINA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PLANO 03</t>
+          <t>PLANO LUXO</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>FUNCIONARIO GRUPO PAX</t>
+          <t>PADRAO ESCRITORIO</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
-      <c r="K26" s="2" t="n">
-        <v>45812</v>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -2106,10 +2040,26 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>CLEONICE PEREIRA DA SILVA</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Wellia de Sousa</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Filtro Inadimplente</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -2119,29 +2069,29 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>102555</v>
+        <v>102544</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SILVANE ALVES BARBOSA DE OLIVEIRA</t>
+          <t>GABRIEL FLEITAS DA SILVA</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>45812</v>
+        <v>45810</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>EDUARDA DE PAULA PASTOR VILELA</t>
+          <t>ANDRESSA HONORIO PEREIRA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO REGIAO 02</t>
+          <t>PARCELAS NOVOS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>PLANO 03</t>
+          <t>PLANO 02 C 2 GAVETAS</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -2149,14 +2099,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO</t>
+          <t>PARCELAS NOVOS</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>45812</v>
+        <v>45811</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2168,10 +2118,26 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>GABRIEL FLEITAS DA SILVA</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Andressa Honorio Pereira</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Indicação de Cliente</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2181,24 +2147,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>102554</v>
+        <v>102545</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ANTONIO MIGUEL ARAUJO LIMA</t>
+          <t>MARIA APARECIDA SEABRA</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>45811</v>
+        <v>45810</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LUCIANA NUNES DA SILVA</t>
+          <t>ANDRESSA HONORIO PEREIRA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PAGSEGURO RECORRENTE</t>
+          <t>BOLETO BANCARIO REGIAO 01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2207,18 +2173,18 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PAGSEGURO RECORRENTE</t>
+          <t>BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>50</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>45812</v>
+        <v>45811</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2230,10 +2196,26 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>MARIA APARECIDA SEABRA</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Andressa Honorio Pereira</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Indicação de Cliente</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -2243,11 +2225,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>102550</v>
+        <v>102552</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EDER LOURENCO CHIMENEZ GABILAN</t>
+          <t>MICHELE LILIANE PEREIRA</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
@@ -2255,12 +2237,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MARIA ROSELI</t>
+          <t>EDUARDA DE PAULA PASTOR VILELA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO REGIAO 01</t>
+          <t>PARCELAS NOVOS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2269,11 +2251,11 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO</t>
+          <t>PARCELAS NOVOS</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -2292,10 +2274,26 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>MICHELE LILIANE PEREIRA DE CASTRO</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Lucas Dos Santos Delgado</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sac</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Ligações</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2305,11 +2303,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>102549</v>
+        <v>102547</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>JOAO BATISTA BERNAL GONZALEZ</t>
+          <t>GISELI SILVA DE SOUZA</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -2317,7 +2315,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MICAELY PAIVA SORRILHA</t>
+          <t>EDUARDA DE PAULA PASTOR VILELA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2331,7 +2329,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2367,33 +2365,33 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>102559</v>
+        <v>102555</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VANDERSON APARECIDO DE SOUZA</t>
+          <t>SILVANE ALVES BARBOSA DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>45783</v>
+        <v>45812</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>NATALIA ZAGHI VITOR</t>
+          <t>EDUARDA DE PAULA PASTOR VILELA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO REGIAO 04</t>
+          <t>BOLETO BANCARIO REGIAO 02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PLANO 02 C 2 GAVETAS</t>
+          <t>PLANO 03</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2401,10 +2399,10 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>45783</v>
+        <v>45812</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2429,19 +2427,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>102548</v>
+        <v>102567</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HALCIONE MOREIRA VINCIGUERA</t>
+          <t>MARIA LUCILENE MAZARIM DA COSTA</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>45811</v>
+        <v>45783</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>VEND.SILAS DE OLIVEIRA</t>
+          <t>EDUARDA DE PAULA PASTOR VILELA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2466,7 +2464,7 @@
         <v>50</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>45812</v>
+        <v>45814</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2480,7 +2478,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>HALCIONE MOREIRA VINCIGUEIRA</t>
+          <t>MARIA LUCILENE MAZARIM DA COSTA</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2507,43 +2505,45 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>102556</v>
+        <v>102554</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CELIA VIEIRA</t>
+          <t>ANTONIO MIGUEL ARAUJO LIMA</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
+        <v>45811</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LUCIANA NUNES DA SILVA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>PAGSEGURO RECORRENTE</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>PLANO 03</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>10</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>PAGSEGURO RECORRENTE</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>50</v>
+      </c>
+      <c r="K33" s="2" t="n">
         <v>45812</v>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>VEND.SILAS DE OLIVEIRA</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>PARCELAS NOVOS</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>PLANO 03</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>28</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>PARCELAS NOVOS</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -2567,43 +2567,45 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>102557</v>
+        <v>102550</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MARCIA DA SILVA RODRIGUES</t>
+          <t>EDER LOURENCO CHIMENEZ GABILAN</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
+        <v>45811</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>MARIA ROSELI</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO REGIAO 01</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>PLANO 02 C 2 GAVETAS</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>25</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>160</v>
+      </c>
+      <c r="K34" s="2" t="n">
         <v>45812</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>VEND.SILAS DE OLIVEIRA</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>PARCELAS NOVOS</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>PLANO 03</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>10</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>PARCELAS NOVOS</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -2627,24 +2629,24 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>102558</v>
+        <v>102549</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EDINALDO NAZARETH DE OLIVEIRA</t>
+          <t>JOAO BATISTA BERNAL GONZALEZ</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>45783</v>
+        <v>45811</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>VEND.SILAS DE OLIVEIRA</t>
+          <t>MICAELY PAIVA SORRILHA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PARCELAS NOVOS</t>
+          <t>FUNCIONARIO GRUPO PAX</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2653,17 +2655,19 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>PARCELAS NOVOS</t>
+          <t>FUNCIONARIO GRUPO PAX</t>
         </is>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" s="2" t="n">
+        <v>45812</v>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -2687,33 +2691,33 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>102551</v>
+        <v>102563</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GILBERTO DOS SANTOS</t>
+          <t>ROSA MARIA VIEIRA FERNANDES</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>45811</v>
+        <v>45783</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>VENDAS DIGITAIS</t>
+          <t>NATALIA ZAGHI VITOR</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO REGIAO 03</t>
+          <t>BOLETO BANCARIO REGIAO 02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>PLANO 03</t>
+          <t>PLANO 02 C 2 GAVETAS</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2721,10 +2725,10 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>45812</v>
+        <v>45814</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2736,26 +2740,10 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>GILBERTO</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Gabriela do Nascimento Souza</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Televendas</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Filtro Inadimplente</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -2765,11 +2753,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>102562</v>
+        <v>102559</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MIRIAN GIMENES DA SILVA</t>
+          <t>VANDERSON APARECIDO DE SOUZA</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -2777,31 +2765,33 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>VENDAS DIGITAIS</t>
+          <t>NATALIA ZAGHI VITOR</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PARCELAS NOVOS</t>
+          <t>BOLETO BANCARIO REGIAO 04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>PLANO 03</t>
+          <t>PLANO 02 C 2 GAVETAS</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>PARCELAS NOVOS</t>
+          <t>BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="inlineStr"/>
+        <v>160</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>45783</v>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -2825,11 +2815,11 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>102561</v>
+        <v>102570</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PRISCILA MELLO DOS SANTOS</t>
+          <t>MARISTELA CANISSO VALESE</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -2837,31 +2827,33 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>VENDAS DIGITAIS</t>
+          <t>TAINARA RIBEIRO BRAGA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO REGIAO 02</t>
+          <t>PARCELAS NOVOS</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>PLANO 03</t>
+          <t>PLANO 02 C 2 GAVETAS</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO</t>
+          <t>PARCELAS NOVOS</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr"/>
+        <v>160</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>45814</v>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -2872,10 +2864,26 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>MARISTELA CANISSO</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Luana Mikaela Garcia Da Costa</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Filtro Inadimplente</t>
+        </is>
+      </c>
       <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -2885,11 +2893,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>102560</v>
+        <v>102571</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DAIANE VIEIRA MARTINS</t>
+          <t>ELIZEU OLIVEIRA DIAS</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -2897,12 +2905,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>VENDAS DIGITAIS</t>
+          <t>TAINARA RIBEIRO BRAGA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO REGIAO 02</t>
+          <t>PARCELAS NOVOS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2915,13 +2923,15 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO</t>
+          <t>PARCELAS NOVOS</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>45814</v>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -2945,29 +2955,29 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>102539</v>
+        <v>102568</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MARIA NADIR HAVEROTH</t>
+          <t>MARIA NILZA ALMINO</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>45810</v>
+        <v>45783</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>VITORIA ALVES DA SILVA</t>
+          <t>TAINARA RIBEIRO BRAGA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO REGIAO 02</t>
+          <t>BOLETO BANCARIO REGIAO 03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>PLANO 02 C 2 GAVETAS</t>
+          <t>PLANO 03</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -2979,10 +2989,10 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>45811</v>
+        <v>45814</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2994,10 +3004,26 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>MARIA NILZA ALMINO</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Andressa Honorio Pereira</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Filtro Inadimplente</t>
+        </is>
+      </c>
       <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -3007,33 +3033,33 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>102542</v>
+        <v>102548</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KLEBER PEREIRA RODRIGUES</t>
+          <t>HALCIONE MOREIRA VINCIGUERA</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>45810</v>
+        <v>45811</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>VITORIA ALVES DA SILVA</t>
+          <t>VEND.SILAS DE OLIVEIRA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO REGIAO 04</t>
+          <t>BOLETO BANCARIO REGIAO 02</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>PLANO 02 C 2 GAVETAS</t>
+          <t>PLANO 03</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3041,10 +3067,10 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>45811</v>
+        <v>45812</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -3056,57 +3082,73 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>HALCIONE MOREIRA VINCIGUEIRA</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Andressa Honorio Pereira</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Filtro Inadimplente</t>
+        </is>
+      </c>
       <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ELDORADO</t>
+          <t>DOURADOS PRIMAVERA</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3673</v>
+        <v>102556</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LUCINEIA CECILIO DE ALMEIDA</t>
+          <t>CELIA VIEIRA</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>45810</v>
+        <v>45812</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MIRIAN ALEIXO SPANAMBERG</t>
+          <t>VEND.SILAS DE OLIVEIRA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ESCRITORIO ELDORADO</t>
+          <t>PARCELAS NOVOS</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>PLANO 01</t>
+          <t>PLANO 03</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>PADRAO ESCRITORIO</t>
+          <t>PARCELAS NOVOS</t>
         </is>
       </c>
       <c r="J42" t="n">
         <v>50</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>45810</v>
+        <v>45814</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -3127,33 +3169,33 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GUAIRA</t>
+          <t>DOURADOS PRIMAVERA</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>9992</v>
+        <v>102557</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MARCIA TERESA FERNANDES</t>
+          <t>MARCIA DA SILVA RODRIGUES</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>45810</v>
+        <v>45812</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CARLA CAMILA TEIXEIRA</t>
+          <t>VEND.SILAS DE OLIVEIRA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>COB.PARCELAS</t>
+          <t>PARCELAS NOVOS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>PLANO SIMPLES</t>
+          <t>PLANO 03</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -3161,14 +3203,14 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COB.PARCELAS</t>
+          <t>PARCELAS NOVOS</t>
         </is>
       </c>
       <c r="J43" t="n">
         <v>50</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>45810</v>
+        <v>45814</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3189,28 +3231,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IGUATEMI</t>
+          <t>DOURADOS PRIMAVERA</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>5303</v>
+        <v>102558</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MARGARETE DA FONSECA GONCALVES</t>
+          <t>EDINALDO NAZARETH DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>45811</v>
+        <v>45783</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>VENDAS DIGITAIS</t>
+          <t>VEND.SILAS DE OLIVEIRA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO IGUATEMI</t>
+          <t>PARCELAS NOVOS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3219,18 +3261,18 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO IGUATEMI</t>
+          <t>PARCELAS NOVOS</t>
         </is>
       </c>
       <c r="J44" t="n">
         <v>50</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>45812</v>
+        <v>45814</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3251,19 +3293,19 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IGUATEMI</t>
+          <t>DOURADOS PRIMAVERA</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5301</v>
+        <v>102566</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>JAINE DOS SANTOS ROCHA DA SILVA</t>
+          <t>WANIA ALINE CHAVES</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>45811</v>
+        <v>45812</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -3272,26 +3314,28 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO IGUATEMI</t>
+          <t>BOLETO BANCARIO REGIAO 04</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>PLANO 03</t>
+          <t>PLANO 02 C 2 GAVETAS</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO IGUATEMI</t>
+          <t>BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr"/>
+        <v>160</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>45814</v>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -3304,22 +3348,22 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>JAINE DOS SANTOS ROCHA DA SILVA</t>
+          <t>WANIA ALINE CHAVES</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Lucas Dos Santos Delgado</t>
+          <t>Sheila Licia Nascimento Silva</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sac</t>
+          <t>Televendas</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Plataforma People</t>
+          <t>Filtro Inadimplente</t>
         </is>
       </c>
       <c r="R45" t="inlineStr"/>
@@ -3327,33 +3371,33 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ITAPORA</t>
+          <t>DOURADOS PRIMAVERA</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31896</v>
+        <v>102572</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MARCOS DE FREITAS BARBOSA</t>
+          <t>MARCELO MARQUES DE FREITAS SILVA</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>45812</v>
+        <v>45783</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ELINAY RAYSSA BENITES PORTO</t>
+          <t>VENDAS DIGITAIS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO</t>
+          <t>BOLETO BANCARIO REGIAO 02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>PLANO LUXO</t>
+          <t>PLANO 02 C 2 GAVETAS</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -3361,14 +3405,14 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>PADRAO BOLETO</t>
+          <t>BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>45812</v>
+        <v>45814</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3380,42 +3424,58 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>MARCELO MARQUES DE FREITAS SILVA</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Andressa Honorio Pereira</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Filtro Inadimplente</t>
+        </is>
+      </c>
       <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ITAPORA</t>
+          <t>DOURADOS PRIMAVERA</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31897</v>
+        <v>102564</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ANDREI MIRANDA ROSOLEN</t>
+          <t>SIMONE EMIDIO ONOFRE</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>45812</v>
+        <v>45783</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RAFAEL BRITO</t>
+          <t>VENDAS DIGITAIS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>COB.RAFAEL BRITO CANDIDO</t>
+          <t>BOLETO BANCARIO REGIAO 02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>PLANO LUXO</t>
+          <t>PLANO 02 C 2 GAVETAS</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -3423,14 +3483,14 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>DIA 10 RAFAEL</t>
+          <t>BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>45812</v>
+        <v>45814</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3442,42 +3502,58 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>SIMONE EMIDIO ONOFRE</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Luana Mikaela Garcia Da Costa</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Indicação - Recepções</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Dourados</t>
+        </is>
+      </c>
       <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>JUTI</t>
+          <t>DOURADOS PRIMAVERA</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>24402</v>
+        <v>102574</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JACIRA SILVA IGABRIDAO</t>
+          <t>NEDINA FERREIRA CORREA</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>45812</v>
+        <v>45783</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ANA BEATRIZ DO PRADO SCAVONE</t>
+          <t>VENDAS DIGITAIS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>COB.PARCELAS</t>
+          <t>BOLETO BANCARIO REGIAO 03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>PAX PLANO 3</t>
+          <t>PLANO 02 C 2 GAVETAS</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -3485,13 +3561,15 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>COB.PARCELA</t>
+          <t>BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr"/>
+        <v>160</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>45814</v>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -3502,42 +3580,58 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>NEDINA FERREIRA CORREA</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Sheila Licia Nascimento Silva</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Indicação de Cliente</t>
+        </is>
+      </c>
       <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LAGUNA</t>
+          <t>DOURADOS PRIMAVERA</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26849</v>
+        <v>102565</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GRACIELI CAETANO TAMANHO</t>
+          <t>MONIQUE FIORAVANTI SANSAO BAZAN</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>45810</v>
+        <v>45783</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RAISSA GONCALVES</t>
+          <t>VENDAS DIGITAIS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>COB.ESCRITORIO LAGUNA CARAPA</t>
+          <t>BOLETO BANCARIO REGIAO 03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>PLANO LUXO 03</t>
+          <t>PLANO 02 C 2 GAVETAS</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -3545,14 +3639,14 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>PADRAO ESCRITORIO</t>
+          <t>BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>45810</v>
+        <v>45814</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3564,24 +3658,40 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>MONIQUE FIORAVANTI SANSÃO BAZAN</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Allison Vinicius Lopes Camilo</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Pessoal</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MARECHAL</t>
+          <t>DOURADOS PRIMAVERA</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7299</v>
+        <v>102551</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>VANESA GEMNICZAK</t>
+          <t>GILBERTO DOS SANTOS</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
@@ -3589,17 +3699,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ANA CAROLINA ALTMANN</t>
+          <t>VENDAS DIGITAIS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO MARECHAL</t>
+          <t>BOLETO BANCARIO REGIAO 03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>PLANO SIMPLES</t>
+          <t>PLANO 03</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -3607,13 +3717,11 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO MARECHAL</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>83,5</t>
-        </is>
+          <t>BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>50</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>45812</v>
@@ -3628,42 +3736,58 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>GILBERTO</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Gabriela do Nascimento Souza</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Filtro Inadimplente</t>
+        </is>
+      </c>
       <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MARECHAL</t>
+          <t>DOURADOS PRIMAVERA</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7298</v>
+        <v>102562</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MYCAELA CRISTINA PEREIRA GRUTZMANN</t>
+          <t>MIRIAN GIMENES DA SILVA</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>45811</v>
+        <v>45783</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ANDRESSA VIVIANE GROSKLASS</t>
+          <t>VENDAS DIGITAIS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>COB.ESCRITORIO MARECHAL</t>
+          <t>PARCELAS NOVOS</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>PLANO TRES</t>
+          <t>PLANO 03</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -3671,14 +3795,14 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>COB.ESCRITORIO MARECHAL</t>
+          <t>PARCELAS NOVOS</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>45811</v>
+        <v>45814</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3690,57 +3814,73 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>MIRIAN</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Lucas Dos Santos Delgado</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Cobrador - Ms</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>ANTONIO MARCOS RENOVATO</t>
+        </is>
+      </c>
       <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MARECHAL</t>
+          <t>DOURADOS PRIMAVERA</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7300</v>
+        <v>102573</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ANGELICA MUHLBEIER</t>
+          <t>MARY LUCI SANTOS DE SOUZA</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>45812</v>
+        <v>45783</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>DANIELI DUNCKE</t>
+          <t>VENDAS DIGITAIS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>COB.GLADES BRAWERS</t>
+          <t>BOLETO BANCARIO REGIAO 01</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>PLANO TRES</t>
+          <t>PLANO 03</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>DIA 09 - MARGARIDA</t>
+          <t>BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>45812</v>
+        <v>45814</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3752,24 +3892,40 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>MARY LUCI SANTOS DE SOUZA</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Luana Mikaela Garcia Da Costa</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Indicação - Recepções</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Dourados</t>
+        </is>
+      </c>
       <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MARECHAL</t>
+          <t>DOURADOS PRIMAVERA</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7301</v>
+        <v>102561</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GELSO DOS SANTOS ROCHA</t>
+          <t>PRISCILA MELLO DOS SANTOS</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
@@ -3777,34 +3933,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>DANIELI DUNCKE</t>
+          <t>VENDAS DIGITAIS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO MARECHAL</t>
+          <t>BOLETO BANCARIO REGIAO 02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>PLANO TRES</t>
+          <t>PLANO 03</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO MARECHAL</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>101,5</t>
-        </is>
+          <t>BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>50</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>45783</v>
+        <v>45814</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3816,37 +3970,53 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>PRISCILA MELLO DOS SANTOS FREITAS</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Lucas Dos Santos Delgado</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Contatos do telefone</t>
+        </is>
+      </c>
       <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NAVIRAI</t>
+          <t>DOURADOS PRIMAVERA</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>13835</v>
+        <v>102560</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ROSANGELA MARIA BIZERRA RODRIGUES</t>
+          <t>DAIANE VIEIRA MARTINS</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>45810</v>
+        <v>45783</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ANA BEATRIZ DO PRADO SCAVONE</t>
+          <t>VENDAS DIGITAIS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>COB.ALISON DE SOUZA</t>
+          <t>BOLETO BANCARIO REGIAO 02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3859,14 +4029,14 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>DIA 10 ALISON</t>
+          <t>BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="J54" t="n">
         <v>50</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>45811</v>
+        <v>45814</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3878,42 +4048,58 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>DAIANE VIEIRA MARTINS</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Lucas Dos Santos Delgado</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Sac</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Plataforma People</t>
+        </is>
+      </c>
       <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NAVIRAI</t>
+          <t>DOURADOS PRIMAVERA</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>13836</v>
+        <v>102539</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BIANCA DE AGUIAR RODRIGUES</t>
+          <t>MARIA NADIR HAVEROTH</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>45811</v>
+        <v>45810</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ANA BEATRIZ DO PRADO SCAVONE</t>
+          <t>VITORIA ALVES DA SILVA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO NAVIRAI</t>
+          <t>BOLETO BANCARIO REGIAO 02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>PLANO 03</t>
+          <t>PLANO 02 C 2 GAVETAS</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -3921,14 +4107,14 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO NAVIRAI</t>
+          <t>BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>45812</v>
+        <v>45811</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3949,47 +4135,49 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NOVA ALVORADA</t>
+          <t>DOURADOS PRIMAVERA</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>6813</v>
+        <v>102542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>THAISY MENDES DA CONCEICAO</t>
+          <t>KLEBER PEREIRA RODRIGUES</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
+        <v>45810</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>VITORIA ALVES DA SILVA</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO REGIAO 04</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>PLANO 02 C 2 GAVETAS</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>22</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>160</v>
+      </c>
+      <c r="K56" s="2" t="n">
         <v>45811</v>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>VENDAS DIGITAIS</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>COB.BOLETOS</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>PAX PLANO LUXO 3</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>10</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>PADRAO BOLETO</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -4000,75 +4188,57 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>THAISY MENDES DA CONCEIÇÃO</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>Lucas Dos Santos Delgado</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Televendas</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NOVA IGUACU</t>
+          <t>ELDORADO</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10053</v>
+        <v>3673</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IZABEL CRISTINA FERREIRA ALVES</t>
+          <t>LUCINEIA CECILIO DE ALMEIDA</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>45812</v>
+        <v>45810</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>TALITA JUNIA DA CONCEICAO SILVA</t>
+          <t>MIRIAN ALEIXO SPANAMBERG</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>COB.BOLETO BANCARIO</t>
+          <t>ESCRITORIO ELDORADO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>PLANO II</t>
+          <t>PLANO 01</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>COBRADOR BOLETO BANCARIO</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>126,5</t>
-        </is>
+          <t>PADRAO ESCRITORIO</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>50</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>45812</v>
+        <v>45810</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -4089,15 +4259,15 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NOVA IGUACU</t>
+          <t>GUAIRA</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10052</v>
+        <v>9992</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>EDILSON ABILIO DA SILVA</t>
+          <t>MARCIA TERESA FERNANDES</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
@@ -4105,31 +4275,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>VANESSA CANDIDO DA SILVA ATANAZIO</t>
+          <t>CARLA CAMILA TEIXEIRA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>COB.BOLETO BANCARIO</t>
+          <t>COB.PARCELAS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>PLANO II</t>
+          <t>PLANO SIMPLES</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>COBRADOR BOLETO BANCARIO</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>101,5</t>
-        </is>
+          <t>COB.PARCELAS</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>50</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>45810</v>
@@ -4153,47 +4321,49 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NOVA IGUACU</t>
+          <t>IGUATEMI</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10054</v>
+        <v>5306</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>QUELZA CRISTINA DE LEMOS COSTA</t>
+          <t>RENATA KERLE GONCALVES GARCIA</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>45812</v>
+        <v>45783</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>VENDAS DIGITAIS</t>
+          <t>EMELY SARA NOGUEIRA CAVALCANTE</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>COB.BOLETO BANCARIO</t>
+          <t>BOLETO BANCARIO IGUATEMI</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>PLANO III</t>
+          <t>PLANO 03</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>COBRADOR BOLETO BANCARIO</t>
+          <t>BOLETO BANCARIO IGUATEMI</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>45814</v>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -4213,41 +4383,41 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PONTA PORA COBRANCA</t>
+          <t>IGUATEMI</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>32032</v>
+        <v>5305</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ANA MARIA NASCIMENTO MARIANO</t>
+          <t>DANIELI OLIVEIRA LIMA</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>45810</v>
+        <v>45783</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ANDRE MENOSSI</t>
+          <t>EMELY SARA NOGUEIRA CAVALCANTE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO PONTA PORA</t>
+          <t>BOLETO BANCARIO IGUATEMI</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>PLANO LUXO</t>
+          <t>PLANO 03</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>COB.BOLETO</t>
+          <t>BOLETO BANCARIO IGUATEMI</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -4273,47 +4443,49 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PONTA PORA COBRANCA</t>
+          <t>IGUATEMI</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>32033</v>
+        <v>5303</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>JADSON OLIVEIRA RECALDE</t>
+          <t>MARGARETE DA FONSECA GONCALVES</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>45810</v>
+        <v>45811</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ANDRE MENOSSI</t>
+          <t>VENDAS DIGITAIS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>COB.PARCELAS NOVOS</t>
+          <t>BOLETO BANCARIO IGUATEMI</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>PLANO LUXO</t>
+          <t>PLANO 03</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>COB.PARCELAS NOVOS</t>
+          <t>BOLETO BANCARIO IGUATEMI</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>45812</v>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -4333,15 +4505,15 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PONTA PORA COBRANCA</t>
+          <t>IGUATEMI</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>32034</v>
+        <v>5301</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NELSON TELES DA SILVA</t>
+          <t>JAINE DOS SANTOS ROCHA DA SILVA</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
@@ -4349,17 +4521,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ANDRE MENOSSI</t>
+          <t>VENDAS DIGITAIS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO PONTA PORA</t>
+          <t>BOLETO BANCARIO IGUATEMI</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>PLANO LUXO</t>
+          <t>PLANO 03</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -4367,7 +4539,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>COB.BOLETO</t>
+          <t>BOLETO BANCARIO IGUATEMI</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -4384,42 +4556,58 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>JAINE DOS SANTOS ROCHA DA SILVA</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Lucas Dos Santos Delgado</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Sac</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Plataforma People</t>
+        </is>
+      </c>
       <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PONTA PORA COBRANCA</t>
+          <t>ITAPORA</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>32038</v>
+        <v>31896</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>JACIANE WIECZOREK</t>
+          <t>MARCOS DE FREITAS BARBOSA</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>45783</v>
+        <v>45812</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>EVELYN DORNELES RODRIGUES</t>
+          <t>ELINAY RAYSSA BENITES PORTO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>COB.ESCRITORIO PONTA PORA</t>
+          <t>BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>PLANO SUPER LUXO</t>
+          <t>PLANO LUXO</t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -4427,13 +4615,15 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>COB.ESCRITORIO PONTA PORA</t>
+          <t>PADRAO BOLETO</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>45812</v>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -4453,15 +4643,15 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PONTA PORA COBRANCA</t>
+          <t>ITAPORA</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>32036</v>
+        <v>31897</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MATEUS NAPOLEAO ANDRE</t>
+          <t>ANDREI MIRANDA ROSOLEN</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
@@ -4469,12 +4659,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>VENDAS DIGITAIS</t>
+          <t>RAFAEL BRITO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO PONTA PORA</t>
+          <t>COB.RAFAEL BRITO CANDIDO</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4487,7 +4677,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>COB.BOLETO</t>
+          <t>DIA 10 RAFAEL</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -4506,58 +4696,42 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>MATEUS NAPOLEAO ANDRE</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>Lucas Dos Santos Delgado</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Sac</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>Plataforma People</t>
-        </is>
-      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PONTA PORA COBRANCA</t>
+          <t>ITAQUIRAI</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>32035</v>
+        <v>3927</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GILCILANE RIQUELME DOS SANTOS SILVA</t>
+          <t>LUCIANA OLIVEIRA DOS SANTOS PADUINA</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>45812</v>
+        <v>45783</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>VENDAS DIGITAIS</t>
+          <t>CARINE FERNANDA DE MATOS PUTON</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO PONTA PORA</t>
+          <t>COB.PARCELAS</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>PLANO LUXO</t>
+          <t>PLANO 03</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -4565,14 +4739,14 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>COB.BOLETO</t>
+          <t>COB. PARCELAS</t>
         </is>
       </c>
       <c r="J65" t="n">
         <v>50</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>45812</v>
+        <v>45814</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -4593,15 +4767,15 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PONTA PORA COBRANCA</t>
+          <t>JUTI</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>32037</v>
+        <v>24402</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LUCIENE DOS SANTOS SOUZA</t>
+          <t>JACIRA SILVA IGABRIDAO</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
@@ -4609,17 +4783,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>VENDAS DIGITAIS</t>
+          <t>ANA BEATRIZ DO PRADO SCAVONE</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>COB.PARCELAS NOVOS</t>
+          <t>COB.PARCELAS</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>PLANO LUXO</t>
+          <t>PAX PLANO 3</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -4627,14 +4801,14 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>COB.PARCELAS NOVOS</t>
+          <t>COB.PARCELA</t>
         </is>
       </c>
       <c r="J66" t="n">
         <v>50</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>45812</v>
+        <v>45814</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -4655,33 +4829,33 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>RIBAS DO RIO PARDO</t>
+          <t>LAGUNA</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>790</v>
+        <v>26849</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>VALDEMIR DIAS BUENO</t>
+          <t>GRACIELI CAETANO TAMANHO</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>45783</v>
+        <v>45810</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>EVELYN JENNIFER IFRAN DA SILVA</t>
+          <t>RAISSA GONCALVES</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO RIBAS</t>
+          <t>COB.ESCRITORIO LAGUNA CARAPA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>PLANO UNICO</t>
+          <t>PLANO LUXO 03</t>
         </is>
       </c>
       <c r="H67" t="n">
@@ -4689,13 +4863,15 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ROTA PADRAO</t>
+          <t>PADRAO ESCRITORIO</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>45810</v>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -4715,33 +4891,33 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>RIO BRILHANTE</t>
+          <t>MARECHAL</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>11468</v>
+        <v>7299</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CLAUDECIR TAVARES DE OLIVEIRA</t>
+          <t>VANESA GEMNICZAK</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>45810</v>
+        <v>45811</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>BIANCA LAURIELI MOREIRA AQUINO</t>
+          <t>ANA CAROLINA ALTMANN</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>COB.REGIELI DE SOUZA SOARES</t>
+          <t>BOLETO BANCARIO MARECHAL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>PLANO LUXO</t>
+          <t>PLANO SIMPLES</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -4749,11 +4925,13 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>DIA 10</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
-        <v>50</v>
+          <t>BOLETO BANCARIO MARECHAL</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>83,5</t>
+        </is>
       </c>
       <c r="K68" s="2" t="n">
         <v>45812</v>
@@ -4777,48 +4955,48 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RIO BRILHANTE</t>
+          <t>MARECHAL</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>11469</v>
+        <v>7298</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>JOSIAS JOSE DA SILVA</t>
+          <t>MYCAELA CRISTINA PEREIRA GRUTZMANN</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>45810</v>
+        <v>45811</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>JULIA BEATRIZ SOARES</t>
+          <t>ANDRESSA VIVIANE GROSKLASS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO RIO BRILHANTE</t>
+          <t>COB.ESCRITORIO MARECHAL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>PLANO LUXO</t>
+          <t>PLANO TRES</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>PADRAO BOLETO BANCARIO</t>
+          <t>COB.ESCRITORIO MARECHAL</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>45812</v>
+        <v>45811</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4839,48 +5017,48 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>RIO BRILHANTE</t>
+          <t>MARECHAL</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>11467</v>
+        <v>7300</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>JACIRA CRISPIN DA FONSECA</t>
+          <t>ANGELICA MUHLBEIER</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>45810</v>
+        <v>45812</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SONIA MARIA MARTINS</t>
+          <t>DANIELI DUNCKE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO RIO BRILHANTE</t>
+          <t>COB.GLADES BRAWERS</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>PLANO LUXO</t>
+          <t>PLANO TRES</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>PADRAO BOLETO BANCARIO</t>
+          <t>DIA 09 - MARGARIDA</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>45811</v>
+        <v>45812</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4901,15 +5079,15 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>RIO BRILHANTE</t>
+          <t>MARECHAL</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>11472</v>
+        <v>7301</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>JULIO CESAR GALDINO DA CONCEICAO</t>
+          <t>GELSO DOS SANTOS ROCHA</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
@@ -4917,31 +5095,35 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SONIA MARIA MARTINS</t>
+          <t>DANIELI DUNCKE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ESCRITORIO RIO BRILHANTE</t>
+          <t>BOLETO BANCARIO MARECHAL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>PLANO LUXO</t>
+          <t>PLANO TRES</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>PADRAO ESCRITORIO</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="inlineStr"/>
+          <t>BOLETO BANCARIO MARECHAL</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>101,5</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>45783</v>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -4961,48 +5143,48 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>RIO BRILHANTE</t>
+          <t>NAVIRAI</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>11470</v>
+        <v>13835</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>LUCINETE DA COSTA SILVA</t>
+          <t>ROSANGELA MARIA BIZERRA RODRIGUES</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>45811</v>
+        <v>45810</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>VENDAS DIGITAIS</t>
+          <t>ANA BEATRIZ DO PRADO SCAVONE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>COB.PARCELAS</t>
+          <t>COB.ALISON DE SOUZA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>PLANO LUXO</t>
+          <t>PLANO 03</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>COB.PARCELAS</t>
+          <t>DIA 10 ALISON</t>
         </is>
       </c>
       <c r="J72" t="n">
         <v>50</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>45812</v>
+        <v>45811</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -5014,72 +5196,58 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>LUCINETE D COSTA SILVA</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>Lucas Dos Santos Delgado</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Televendas</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>RIO BRILHANTE</t>
+          <t>NAVIRAI</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>11471</v>
+        <v>13836</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>JOSIANE MARTINS MENDONCA LOPES</t>
+          <t>BIANCA DE AGUIAR RODRIGUES</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>45810</v>
+        <v>45811</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>VITORIA SILVA SANTOS</t>
+          <t>ANA BEATRIZ DO PRADO SCAVONE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO RIO BRILHANTE</t>
+          <t>BOLETO BANCARIO NAVIRAI</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>PLANO LUXO</t>
+          <t>PLANO 03</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>PADRAO BOLETO BANCARIO</t>
+          <t>BOLETO BANCARIO NAVIRAI</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>45812</v>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -5090,72 +5258,58 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>JOSIANE MARTINS MENDONÇA LOPES</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>Andressa Honorio Pereira</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Televendas</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>Filtro Inadimplente</t>
-        </is>
-      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SAO GABRIEL</t>
+          <t>NAVIRAI</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>4810</v>
+        <v>13837</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ROSANGELA TEODORO DE FREITAS</t>
+          <t>NARCISO CANDIDO DE SOUZA</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>45811</v>
+        <v>45783</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>VENDAS DIGITAIS</t>
+          <t>ANA BEATRIZ DO PRADO SCAVONE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO</t>
+          <t>BOLETO BANCARIO NAVIRAI</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>PLANO LUXO</t>
+          <t>PLANO 03</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>PADRAO BOLETO BANCARIO</t>
+          <t>BOLETO BANCARIO NAVIRAI</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>45814</v>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>NOVO</t>
@@ -5166,70 +5320,54 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>ROSANGELA TEODORO DE FREITAS</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>Sheila Licia Nascimento Silva</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Televendas</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>Indicação de Cliente</t>
-        </is>
-      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SORRISO-MT</t>
+          <t>NOVA ALVORADA</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>13309</v>
+        <v>6814</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CLAUDEMILSON ALVES FERREIRA</t>
+          <t>HEMERSON CABRAL VEGA</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>45810</v>
+        <v>45783</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ANA CAROLINA DECARO DIAS DE SOUZA</t>
+          <t>EDSON DE SOUZA MATOS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO SORRISO</t>
+          <t>COB.BOLETOS</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>PLANO 2 - SORRISO</t>
+          <t>PAX PLANO LUXO 3</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO</t>
+          <t>PADRAO BOLETO</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>45783</v>
@@ -5253,15 +5391,15 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SORRISO-MT</t>
+          <t>NOVA ALVORADA</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>13310</v>
+        <v>6813</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LEONILDA KOLAKOWSKI RIBOLDI</t>
+          <t>THAISY MENDES DA CONCEICAO</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
@@ -5269,34 +5407,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>BIANCA OLIVEIRA</t>
+          <t>VENDAS DIGITAIS</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>WEIDY_Z.N._01_VERMELHO</t>
+          <t>COB.BOLETOS</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>PLANO 03 SORRISO</t>
+          <t>PAX PLANO LUXO 3</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>PADRAO WEIDE</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>101,5</t>
-        </is>
+          <t>PADRAO BOLETO</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>50</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>45812</v>
+        <v>45814</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -5308,24 +5444,40 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>THAISY MENDES DA CONCEIÇÃO</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Lucas Dos Santos Delgado</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
       <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SORRISO-MT</t>
+          <t>NOVA IGUACU</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>13311</v>
+        <v>10054</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>DIRCE APARECIDA DOS SANTOS</t>
+          <t>QUELZA CRISTINA DE LEMOS COSTA</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
@@ -5333,34 +5485,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>BIANCA OLIVEIRA</t>
+          <t>TALITA JUNIA DA CONCEICAO SILVA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO SORRISO</t>
+          <t>COB.BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>PLANO 03 SORRISO</t>
+          <t>PLANO II</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO</t>
+          <t>COBRADOR BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>101,5</t>
+          <t>126,5</t>
         </is>
       </c>
       <c r="K77" s="2" t="n">
-        <v>45783</v>
+        <v>45814</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -5381,48 +5533,50 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SORRISO-MT</t>
+          <t>NOVA IGUACU</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>13308</v>
+        <v>10053</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SOLANGE SOARES DOS SANTOS MARTINS BORGES</t>
+          <t>IZABEL CRISTINA FERREIRA ALVES</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>45810</v>
+        <v>45812</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>BIANCA OLIVEIRA</t>
+          <t>TALITA JUNIA DA CONCEICAO SILVA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>WEIDY_Z.N._01_VERMELHO</t>
+          <t>COB.BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>PLANO 2 - SORRISO</t>
+          <t>PLANO II</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>PADRAO WEIDE</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
-        <v>325</v>
+          <t>COBRADOR BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>126,5</t>
+        </is>
       </c>
       <c r="K78" s="2" t="n">
-        <v>45811</v>
+        <v>45812</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -5443,48 +5597,50 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SORRISO-MT</t>
+          <t>NOVA IGUACU</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>13306</v>
+        <v>10057</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>VALMIR LOPES</t>
+          <t>SARAH DE SOUZA REIS</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>45810</v>
+        <v>45783</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>BIANCA OLIVEIRA</t>
+          <t>TALITA JUNIA DA CONCEICAO SILVA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>LUCILIA_Z.L._03_ VERDE</t>
+          <t>COB.BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>PLANO 2 - SORRISO</t>
+          <t>PLANO II</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>PADRAO LUCILIA</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
-        <v>65</v>
+          <t>COBRADOR BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>101,5</t>
+        </is>
       </c>
       <c r="K79" s="2" t="n">
-        <v>45811</v>
+        <v>45814</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -5505,15 +5661,15 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SORRISO-MT</t>
+          <t>NOVA IGUACU</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>13307</v>
+        <v>10052</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ALEXANDRA TACIANA DRESCH MARQUES DA SILVA</t>
+          <t>EDILSON ABILIO DA SILVA</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
@@ -5521,32 +5677,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>BIANCA OLIVEIRA</t>
+          <t>VANESSA CANDIDO DA SILVA ATANAZIO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO SORRISO</t>
+          <t>COB.BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>PLANO 2 - SORRISO</t>
+          <t>PLANO II</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>BOLETO BANCARIO</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
-        <v>65</v>
+          <t>COBRADOR BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>101,5</t>
+        </is>
       </c>
       <c r="K80" s="2" t="n">
-        <v>45811</v>
+        <v>45810</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -5565,361 +5723,599 @@
       <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>NOVA IGUACU</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>10056</v>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LUCAS HENRIQUE</t>
+          <t>ROSANGELA BAPTISTA DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
         <v>45783</v>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>VENDAS DIGITAIS</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>COB.BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>PLANO II</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>10</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>COBRADOR BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>Sheila Licia Nascimento Silva</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Televendas</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>Filtro Inadimplente</t>
-        </is>
-      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>NOVA IGUACU</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>10055</v>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SÔNIA GREFFE CHAVES</t>
+          <t>EDILENE CORREIA DE LIRA</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
         <v>45783</v>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>VENDAS DIGITAIS</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>COB.BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>PLANO II</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>10</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>COBRADOR BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>Andressa Honorio Pereira</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Televendas</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>Indicação de Cliente</t>
-        </is>
-      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr"/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PJC</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>27991</v>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GISLAINE LOPES DA SILVA</t>
+          <t>ISABEL VEGA RUIZ</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
         <v>45783</v>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>DIANA ELIZABETH FERREIRA PALACIOS</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>COB.JUAN JAVIER ALMADA ARMOA</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>PLANO BASICO</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>10</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>DIA 10</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>Sheila Licia Nascimento Silva</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Televendas</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>Indicação de Cliente</t>
-        </is>
-      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PJC</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>27990</v>
+      </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IZOLDINO ALVES</t>
+          <t>EVA CELIA DELGADO BRITEZ</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
         <v>45783</v>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>VEND.ANA BENITEZ</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>COB.EFRAIN</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>PLANO BASICO</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>10</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>DIA 10</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>Luana Mikaela Garcia Da Costa</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Televendas</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>Filtro Inadimplente</t>
-        </is>
-      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PJC</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>27993</v>
+      </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PIETRA</t>
+          <t>SARA ELENA LESME MARQUES</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
         <v>45783</v>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>VEND.ANA BENITEZ</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>COB.EFRAIN</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>PLANO BASICO</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>10</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>DIA 10</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>Sandi Suellen Ferreira</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Televendas</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>Filtro Inadimplente</t>
-        </is>
-      </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PJC</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>27992</v>
+      </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ADELIA ALVES DE MIRANDA</t>
+          <t>BETTY ZUNILDA SALINAS</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
         <v>45783</v>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>VEND.ANA BENITEZ</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>COB.EFRAIN</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>PLANO LUXO</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>27</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>DIA 27</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>Andressa Honorio Pereira</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Televendas</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>Indicação de Cliente</t>
-        </is>
-      </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>PONTA PORA COBRANCA</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>32032</v>
+      </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ELIZEU DIAS</t>
+          <t>ANA MARIA NASCIMENTO MARIANO</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
+        <v>45810</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ANDRE MENOSSI</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO PONTA PORA</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>PLANO LUXO</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>21</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>COB.BOLETO</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PONTA PORA COBRANCA</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>32033</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>JADSON OLIVEIRA RECALDE</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>45810</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ANDRE MENOSSI</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>COB.PARCELAS NOVOS</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>PLANO LUXO</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>10</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>COB.PARCELAS NOVOS</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>PONTA PORA COBRANCA</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>32034</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>NELSON TELES DA SILVA</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>45811</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ANDRE MENOSSI</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO PONTA PORA</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>PLANO LUXO</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>10</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>COB.BOLETO</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>PONTA PORA COBRANCA</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>32038</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>JACIANE WIECZOREK</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
         <v>45783</v>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>Gabriela do Nascimento Souza</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Televendas</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>Filtro Inadimplente</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>WANIA ALINE CHAVES</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="n">
-        <v>45783</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>Sheila Licia Nascimento Silva</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Televendas</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>Filtro Inadimplente</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>ALICE RAQUEL</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="n">
-        <v>45783</v>
-      </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>Luana Mikaela Garcia Da Costa</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Televendas</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>Filtro Inadimplente</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>EVELYN DORNELES RODRIGUES</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>COB.ESCRITORIO PONTA PORA</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>PLANO SUPER LUXO</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>10</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>COB.ESCRITORIO PONTA PORA</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
@@ -5927,19 +6323,59 @@
       <c r="R90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>PONTA PORA COBRANCA</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>32039</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>THAINARA BIANCA AJALA ZABALLOS</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>45783</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>MAYRA ALMEIDA SILVA</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>COB.ESCRITORIO PONTA PORA</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>PLANO LUXO</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>10</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>COB.ESCRITORIO PONTA PORA</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
@@ -5947,39 +6383,139 @@
       <c r="R91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>PONTA PORA COBRANCA</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>32036</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>MATEUS NAPOLEAO ANDRE</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>45812</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>VENDAS DIGITAIS</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO PONTA PORA</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>PLANO LUXO</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>10</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>COB.BOLETO</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>50</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>45812</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>MATEUS NAPOLEAO ANDRE</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Lucas Dos Santos Delgado</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Sac</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Plataforma People</t>
+        </is>
+      </c>
       <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>PONTA PORA COBRANCA</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>32035</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>GILCILANE RIQUELME DOS SANTOS SILVA</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>45812</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>VENDAS DIGITAIS</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO PONTA PORA</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>PLANO LUXO</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>10</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>COB.BOLETO</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>50</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>45812</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
@@ -5987,19 +6523,61 @@
       <c r="R93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
-      <c r="B94" t="inlineStr"/>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>PONTA PORA COBRANCA</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>32037</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>LUCIENE DOS SANTOS SOUZA</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>45812</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>VENDAS DIGITAIS</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>COB.PARCELAS NOVOS</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>PLANO LUXO</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>10</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>COB.PARCELAS NOVOS</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>50</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>45812</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
@@ -6007,19 +6585,59 @@
       <c r="R94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>RIBAS DO RIO PARDO</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>790</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>VALDEMIR DIAS BUENO</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>45783</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>EVELYN JENNIFER IFRAN DA SILVA</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO RIBAS</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>PLANO UNICO</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>10</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>ROTA PADRAO</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
@@ -6027,19 +6645,59 @@
       <c r="R95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
-      <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>RIBAS DO RIO PARDO</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>791</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>IZABEL DA CONCEICAO DA SILVA</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>45783</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RONIE MEDEIROS</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO RIBAS</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>PLANO UNICO</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>25</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>ROTA PADRAO</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
@@ -6047,19 +6705,61 @@
       <c r="R96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
-      <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>RIO BRILHANTE</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>11468</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>CLAUDECIR TAVARES DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>45810</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>BIANCA LAURIELI MOREIRA AQUINO</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>COB.REGIELI DE SOUZA SOARES</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>PLANO LUXO</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>10</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>DIA 10</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>50</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>45812</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
@@ -6067,19 +6767,61 @@
       <c r="R97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
-      <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>RIO BRILHANTE</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>11469</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>JOSIAS JOSE DA SILVA</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>45810</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>JULIA BEATRIZ SOARES</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO RIO BRILHANTE</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>PLANO LUXO</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>5</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>PADRAO BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>50</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>45812</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
@@ -6087,19 +6829,61 @@
       <c r="R98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
-      <c r="B99" t="inlineStr"/>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>RIO BRILHANTE</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>11467</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>JACIRA CRISPIN DA FONSECA</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>45810</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>SONIA MARIA MARTINS</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO RIO BRILHANTE</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>PLANO LUXO</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>27</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>PADRAO BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>41</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>45811</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
@@ -6107,19 +6891,59 @@
       <c r="R99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>RIO BRILHANTE</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>11472</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>JULIO CESAR GALDINO DA CONCEICAO</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>45783</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>SONIA MARIA MARTINS</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>ESCRITORIO RIO BRILHANTE</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>PLANO LUXO</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>10</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>PADRAO ESCRITORIO</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
       <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
@@ -6127,39 +6951,137 @@
       <c r="R100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr"/>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>RIO BRILHANTE</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>11470</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>LUCINETE DA COSTA SILVA</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>45811</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>VENDAS DIGITAIS</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>COB.PARCELAS</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>PLANO LUXO</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>5</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>COB.PARCELAS</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>50</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>45812</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>LUCINETE D COSTA SILVA</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Lucas Dos Santos Delgado</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
       <c r="R101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
-      <c r="B102" t="inlineStr"/>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>RIO BRILHANTE</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>11473</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>EVA APARECIDA CONDE LIMA</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>45783</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>VENDAS DIGITAIS</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO RIO BRILHANTE</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>PLANO LUXO</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>10</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>PADRAO BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr"/>
@@ -6167,59 +7089,215 @@
       <c r="R102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
-      <c r="B103" t="inlineStr"/>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>RIO BRILHANTE</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>11471</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>JOSIANE MARTINS MENDONCA LOPES</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>45810</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>VITORIA SILVA SANTOS</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO RIO BRILHANTE</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>PLANO LUXO</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>12</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>PADRAO BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
       <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>JOSIANE MARTINS MENDONÇA LOPES</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Andressa Honorio Pereira</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Filtro Inadimplente</t>
+        </is>
+      </c>
       <c r="R103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
-      <c r="B104" t="inlineStr"/>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SAO GABRIEL</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>4810</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>ROSANGELA TEODORO DE FREITAS</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>45811</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>VENDAS DIGITAIS</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>PLANO LUXO</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>5</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>PADRAO BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>50</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>45814</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>ROSANGELA TEODORO DE FREITAS</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Sheila Licia Nascimento Silva</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>Indicação de Cliente</t>
+        </is>
+      </c>
       <c r="R104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
-      <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>SORRISO-MT</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>13309</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>CLAUDEMILSON ALVES FERREIRA</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>45810</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>ANA CAROLINA DECARO DIAS DE SOUZA</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO SORRISO</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>PLANO 2 - SORRISO</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>10</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>65</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>45783</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
@@ -6227,19 +7305,63 @@
       <c r="R105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>SORRISO-MT</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>13310</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>LEONILDA KOLAKOWSKI RIBOLDI</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>45811</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>BIANCA OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>WEIDY_Z.N._01_VERMELHO</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>PLANO 03 SORRISO</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>6</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>PADRAO WEIDE</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>101,5</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>45812</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
@@ -6247,19 +7369,63 @@
       <c r="R106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
-      <c r="B107" t="inlineStr"/>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>SORRISO-MT</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>13311</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>DIRCE APARECIDA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>45812</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>BIANCA OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO SORRISO</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>PLANO 03 SORRISO</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>15</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>101,5</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>45783</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr"/>
@@ -6267,19 +7433,61 @@
       <c r="R107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
-      <c r="B108" t="inlineStr"/>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SORRISO-MT</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>13308</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SOLANGE SOARES DOS SANTOS MARTINS BORGES</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>45810</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>BIANCA OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>WEIDY_Z.N._01_VERMELHO</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>PLANO 2 - SORRISO</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>15</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>PADRAO WEIDE</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>325</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>45811</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
@@ -6287,19 +7495,61 @@
       <c r="R108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
-      <c r="B109" t="inlineStr"/>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>SORRISO-MT</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>13306</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>VALMIR LOPES</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>45810</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>BIANCA OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>LUCILIA_Z.L._03_ VERDE</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>PLANO 2 - SORRISO</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>12</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>PADRAO LUCILIA</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>65</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>45811</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
@@ -6307,19 +7557,61 @@
       <c r="R109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
-      <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SORRISO-MT</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>13307</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ALEXANDRA TACIANA DRESCH MARQUES DA SILVA</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>45810</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>BIANCA OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO SORRISO</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>PLANO 2 - SORRISO</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>5</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>65</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>45811</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
@@ -6327,19 +7619,61 @@
       <c r="R110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
-      <c r="B111" t="inlineStr"/>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>SORRISO-MT</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>13312</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ROSANA RESENDE</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>45783</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>BIANCA OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO SORRISO</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>PLANO 2 - SORRISO</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>20</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>BOLETO BANCARIO</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>65</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>45814</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
@@ -6349,8 +7683,14 @@
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>LUCAS HENRIQUE</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>45844</v>
+      </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
@@ -6361,16 +7701,34 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Sheila Licia Nascimento Silva</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Filtro Inadimplente</t>
+        </is>
+      </c>
       <c r="R112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SÔNIA GREFFE CHAVES</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>45844</v>
+      </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
@@ -6381,16 +7739,34 @@
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr"/>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Andressa Honorio Pereira</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Indicação de Cliente</t>
+        </is>
+      </c>
       <c r="R113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr"/>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>GISLAINE LOPES DA SILVA</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>45844</v>
+      </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
@@ -6401,16 +7777,34 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Sheila Licia Nascimento Silva</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>Indicação de Cliente</t>
+        </is>
+      </c>
       <c r="R114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr"/>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>IZOLDINO ALVES</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>45844</v>
+      </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
@@ -6421,16 +7815,34 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Luana Mikaela Garcia Da Costa</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>Filtro Inadimplente</t>
+        </is>
+      </c>
       <c r="R115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr"/>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>PIETRA</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>45844</v>
+      </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
@@ -6441,16 +7853,34 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Sandi Suellen Ferreira</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>Filtro Inadimplente</t>
+        </is>
+      </c>
       <c r="R116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr"/>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ADELIA ALVES DE MIRANDA</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>45844</v>
+      </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
@@ -6461,16 +7891,34 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Andressa Honorio Pereira</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>Indicação de Cliente</t>
+        </is>
+      </c>
       <c r="R117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr"/>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ELIZEU DIAS</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>45844</v>
+      </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
@@ -6481,16 +7929,34 @@
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Gabriela do Nascimento Souza</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>Filtro Inadimplente</t>
+        </is>
+      </c>
       <c r="R118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr"/>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ADECINA SILVA LIMA</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>45844</v>
+      </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
@@ -6501,16 +7967,34 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Luana Mikaela Garcia Da Costa</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Indicação - Recepções</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Dourados</t>
+        </is>
+      </c>
       <c r="R119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr"/>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>MARCIO JOSE DOS PASSOS</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>45844</v>
+      </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
@@ -6521,16 +8005,34 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Andressa Honorio Pereira</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>Filtro Inadimplente</t>
+        </is>
+      </c>
       <c r="R120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr"/>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ALICE RAQUEL</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>45844</v>
+      </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
@@ -6541,16 +8043,34 @@
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Luana Mikaela Garcia Da Costa</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>Filtro Inadimplente</t>
+        </is>
+      </c>
       <c r="R121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>BRENDA BALDUINO</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>45844</v>
+      </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
@@ -6561,16 +8081,34 @@
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Sheila Licia Nascimento Silva</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>Indicação de Cliente</t>
+        </is>
+      </c>
       <c r="R122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>JOSE RAMAO DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>45844</v>
+      </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
@@ -6581,9 +8119,21 @@
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Wellia de Sousa</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Televendas</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>Filtro Inadimplente</t>
+        </is>
+      </c>
       <c r="R123" t="inlineStr"/>
     </row>
     <row r="124">

--- a/uploads/resultado.xlsx
+++ b/uploads/resultado.xlsx
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>45844</v>
+        <v>45906</v>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>45844</v>
+        <v>45906</v>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>45844</v>
+        <v>45906</v>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>45844</v>
+        <v>45906</v>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
@@ -7841,7 +7841,7 @@
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>45844</v>
+        <v>45906</v>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>45844</v>
+        <v>45906</v>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
@@ -7917,7 +7917,7 @@
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>45844</v>
+        <v>45906</v>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>45844</v>
+        <v>45906</v>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>45844</v>
+        <v>45906</v>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>45844</v>
+        <v>45906</v>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
@@ -8069,7 +8069,7 @@
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>45844</v>
+        <v>45906</v>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>45844</v>
+        <v>45906</v>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
